--- a/KatalonData/RADTestData/MFInsNumLessThanSixError.xlsx
+++ b/KatalonData/RADTestData/MFInsNumLessThanSixError.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Result</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>Thu Jul 09 23:02:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:46:25 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -485,7 +488,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>

--- a/KatalonData/RADTestData/MFInsNumLessThanSixError.xlsx
+++ b/KatalonData/RADTestData/MFInsNumLessThanSixError.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Result</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>Thu Jul 09 23:02:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:17:52 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -485,7 +488,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
